--- a/DailyStandupMeeting.xlsx
+++ b/DailyStandupMeeting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Testing and Secure Coding/GroupAssignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="389" documentId="8_{85551688-011D-426A-89B3-D88759670DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB130FC0-8E4B-4709-BA9A-1293FBD57CEB}"/>
+  <xr:revisionPtr revIDLastSave="426" documentId="8_{85551688-011D-426A-89B3-D88759670DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EE006E-C24D-4578-BFED-F09361410AA2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{989269EE-47AD-4604-BA2D-335F5F79A16A}"/>
   </bookViews>
@@ -365,7 +365,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -553,36 +553,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -605,40 +575,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -669,7 +611,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -678,24 +620,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -720,15 +652,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -740,6 +663,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -757,10 +695,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1064,9 +998,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="28.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="2" customWidth="1"/>
-    <col min="4" max="8" width="51.28515625" style="2" customWidth="1"/>
+    <col min="2" max="8" width="21.5703125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="14.42578125" style="2"/>
   </cols>
   <sheetData>
@@ -1100,19 +1032,19 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1132,10 +1064,10 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1170,25 +1102,25 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="1"/>
@@ -1210,9 +1142,9 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
-      <c r="B5" s="33"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1226,7 +1158,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="1"/>
@@ -1250,21 +1182,21 @@
     </row>
     <row r="6" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="1"/>
@@ -1286,25 +1218,25 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="11" t="s">
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="1"/>
@@ -1326,9 +1258,9 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
@@ -1338,7 +1270,7 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="8"/>
@@ -1367,20 +1299,20 @@
     <row r="9" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="1"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="15" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
         <v>34</v>
       </c>
       <c r="I9" s="1"/>
@@ -1404,21 +1336,21 @@
     </row>
     <row r="10" spans="1:26" ht="68.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17" t="s">
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="1"/>
@@ -1442,7 +1374,7 @@
     </row>
     <row r="11" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
-      <c r="B11" s="36"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1478,7 +1410,7 @@
     </row>
     <row r="12" spans="1:26" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
-      <c r="B12" s="36"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
@@ -1535,12 +1467,12 @@
     </row>
     <row r="14" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1562,12 +1494,12 @@
     </row>
     <row r="15" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3"/>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1617,12 +1549,12 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1647,12 +1579,12 @@
     </row>
     <row r="18" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -29278,29 +29210,27 @@
   <dimension ref="B2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
-    <col min="5" max="8" width="25.42578125" customWidth="1"/>
+    <col min="2" max="8" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29318,30 +29248,30 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="17" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="12"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="8" t="s">
         <v>33</v>
       </c>
@@ -29352,41 +29282,41 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="34"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="35" t="s">
+    <row r="7" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="11" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
+    <row r="8" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
@@ -29398,46 +29328,46 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29452,7 +29382,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="36"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
@@ -29476,23 +29406,23 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -29507,23 +29437,23 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -29550,31 +29480,27 @@
   <dimension ref="B2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" customWidth="1"/>
-    <col min="7" max="8" width="26.5703125" customWidth="1"/>
+    <col min="2" max="8" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="2:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29592,124 +29518,124 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="33"/>
+    <row r="5" spans="2:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="35"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="39" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="34"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="39" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="2:8" ht="27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="2:8" ht="36" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29724,8 +29650,8 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B12" s="36"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -29748,42 +29674,42 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-    </row>
-    <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" spans="2:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -29807,27 +29733,27 @@
   <dimension ref="B2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="8" width="24.85546875" customWidth="1"/>
+    <col min="2" max="8" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="2:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29844,84 +29770,84 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="32" t="s">
+    <row r="4" spans="2:8" ht="36" x14ac:dyDescent="0.25">
+      <c r="B4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="33"/>
+    <row r="5" spans="2:8" ht="36" x14ac:dyDescent="0.25">
+      <c r="B5" s="35"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="18"/>
+      <c r="F5" s="39"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="34"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="8" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="17"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8" t="s">
         <v>53</v>
@@ -29929,34 +29855,34 @@
     </row>
     <row r="9" spans="2:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="8" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29971,8 +29897,8 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B12" s="36"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -29995,42 +29921,42 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="2:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30058,23 +29984,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="2:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="26"/>
-      <c r="C3" s="28"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -30091,59 +30017,59 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="32" t="s">
+    <row r="4" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="33"/>
+    <row r="5" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="35"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="34"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11"/>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="11" t="s">
@@ -30151,34 +30077,34 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:8" ht="36" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="39"/>
+      <c r="E8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="8" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -30188,40 +30114,40 @@
     </row>
     <row r="9" spans="2:8" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="15"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17" t="s">
+      <c r="E10" s="13"/>
+      <c r="F10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -30229,7 +30155,7 @@
       <c r="E11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -30238,8 +30164,8 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="36"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -30262,42 +30188,42 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/DailyStandupMeeting.xlsx
+++ b/DailyStandupMeeting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Testing and Secure Coding/GroupAssignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="8_{85551688-011D-426A-89B3-D88759670DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EE006E-C24D-4578-BFED-F09361410AA2}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="8_{85551688-011D-426A-89B3-D88759670DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FE926F-30EB-4B33-98B7-565D3308257D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{989269EE-47AD-4604-BA2D-335F5F79A16A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="78">
   <si>
     <t>Question</t>
   </si>
@@ -205,9 +205,6 @@
     <t>Auto tests weren't running properly</t>
   </si>
   <si>
-    <t>Week 4 : 6/10/25 ~ 10/10/25</t>
-  </si>
-  <si>
     <t>Sprint Review</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>Finished Auto tests</t>
   </si>
   <si>
-    <t>Presentation slides</t>
-  </si>
-  <si>
     <t>Last minute documentation</t>
   </si>
   <si>
@@ -256,9 +250,6 @@
     <t>Documentation done</t>
   </si>
   <si>
-    <t>Finished presentation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Finishing off Test Report Conclusion </t>
   </si>
   <si>
@@ -266,6 +257,21 @@
   </si>
   <si>
     <t>Had some issues with github</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Presentation</t>
+  </si>
+  <si>
+    <t>Finished Presentation</t>
+  </si>
+  <si>
+    <t>Week 4 : 6/10/25 ~ 12/10/25</t>
   </si>
 </sst>
 </file>
@@ -365,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -583,11 +589,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -629,6 +644,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -652,10 +675,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -665,20 +695,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,6 +724,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1032,19 +1065,19 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1066,8 +1099,8 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1104,7 +1137,7 @@
     </row>
     <row r="4" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -1119,7 +1152,7 @@
       <c r="F4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="8" t="s">
         <v>20</v>
       </c>
@@ -1144,7 +1177,7 @@
     </row>
     <row r="5" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
-      <c r="B5" s="35"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1215,8 @@
     </row>
     <row r="6" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1220,7 +1253,7 @@
     </row>
     <row r="7" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -1260,7 +1293,7 @@
     </row>
     <row r="8" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
-      <c r="B8" s="29"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
@@ -1299,7 +1332,7 @@
     <row r="9" spans="1:26" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="1"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1336,7 +1369,7 @@
     </row>
     <row r="10" spans="1:26" ht="68.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -1374,7 +1407,7 @@
     </row>
     <row r="11" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1410,7 +1443,7 @@
     </row>
     <row r="12" spans="1:26" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
-      <c r="B12" s="29"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
@@ -1467,12 +1500,12 @@
     </row>
     <row r="14" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
-      <c r="B14" s="15" t="s">
-        <v>56</v>
+      <c r="B14" s="19" t="s">
+        <v>55</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1494,12 +1527,12 @@
     </row>
     <row r="15" spans="1:26" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3"/>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1549,12 +1582,12 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
-      <c r="B17" s="15" t="s">
-        <v>57</v>
+      <c r="B17" s="19" t="s">
+        <v>56</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1579,12 +1612,12 @@
     </row>
     <row r="18" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
-      <c r="B18" s="18" t="s">
-        <v>58</v>
+      <c r="B18" s="22" t="s">
+        <v>57</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -29214,23 +29247,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29248,7 +29281,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -29267,11 +29300,11 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="35"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="34"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="8" t="s">
         <v>33</v>
       </c>
@@ -29282,8 +29315,8 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11"/>
@@ -29297,7 +29330,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -29316,7 +29349,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
@@ -29334,7 +29367,7 @@
     </row>
     <row r="9" spans="2:8" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="11" t="s">
@@ -29350,7 +29383,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -29367,7 +29400,7 @@
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29382,7 +29415,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
@@ -29406,23 +29439,23 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>59</v>
+      <c r="B15" s="22" t="s">
+        <v>58</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -29437,23 +29470,23 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="15" t="s">
-        <v>57</v>
+      <c r="B17" s="19" t="s">
+        <v>56</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>60</v>
+      <c r="B18" s="22" t="s">
+        <v>59</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -29484,23 +29517,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29518,7 +29551,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -29537,13 +29570,13 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="35"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="8"/>
@@ -29552,8 +29585,8 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11" t="s">
@@ -29569,7 +29602,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -29585,12 +29618,12 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
+    <row r="8" spans="2:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="B8" s="35"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="18" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -29604,7 +29637,7 @@
     </row>
     <row r="9" spans="2:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="11" t="s">
@@ -29620,7 +29653,7 @@
       <c r="H9" s="11"/>
     </row>
     <row r="10" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -29635,7 +29668,7 @@
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29650,7 +29683,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
@@ -29674,42 +29707,42 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="15" t="s">
-        <v>57</v>
+      <c r="B17" s="19" t="s">
+        <v>56</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="2:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>61</v>
+      <c r="B18" s="37" t="s">
+        <v>60</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -29737,23 +29770,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -29771,7 +29804,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="36" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -29790,7 +29823,7 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="36" x14ac:dyDescent="0.25">
-      <c r="B5" s="35"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -29798,15 +29831,15 @@
         <v>38</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="39"/>
+      <c r="F5" s="18"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11" t="s">
@@ -29820,7 +29853,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -29839,11 +29872,11 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="39"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="8" t="s">
         <v>50</v>
       </c>
@@ -29855,7 +29888,7 @@
     </row>
     <row r="9" spans="2:8" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="11"/>
@@ -29869,7 +29902,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -29882,7 +29915,7 @@
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -29897,7 +29930,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="27" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
@@ -29921,42 +29954,42 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>68</v>
+      <c r="B15" s="22" t="s">
+        <v>66</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="15" t="s">
-        <v>57</v>
+      <c r="B17" s="19" t="s">
+        <v>56</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="2:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>62</v>
+      <c r="B18" s="37" t="s">
+        <v>61</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -29977,30 +30010,31 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D50EA9-52A9-43FA-A599-959B6893304B}">
-  <dimension ref="B2:H18"/>
+  <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="8" width="22.42578125" customWidth="1"/>
+    <col min="2" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="10" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:10" ht="27" x14ac:dyDescent="0.35">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>55</v>
+      <c r="D2" s="29" t="s">
+        <v>77</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="2:10" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="26"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -30016,9 +30050,15 @@
       <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="35" t="s">
+      <c r="I3" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -30026,20 +30066,24 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>71</v>
+      <c r="H4" s="41"/>
+      <c r="I4" s="8" t="s">
+        <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="35"/>
+      <c r="J4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="32"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -30051,15 +30095,19 @@
         <v>53</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>72</v>
+      <c r="H5" s="41"/>
+      <c r="I5" s="8" t="s">
+        <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="37" t="s">
+      <c r="J5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="33"/>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="11"/>
@@ -30070,14 +30118,18 @@
         <v>53</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>74</v>
+      <c r="H6" s="43"/>
+      <c r="I6" s="11" t="s">
+        <v>71</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
+      <c r="J6" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="34" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -30085,52 +30137,64 @@
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="2:8" ht="36" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
+      <c r="I7" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="44"/>
+    </row>
+    <row r="8" spans="2:10" ht="36" x14ac:dyDescent="0.25">
+      <c r="B8" s="35"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="39"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>66</v>
+      <c r="G8" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="2:8" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="2:10" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="2:8" ht="54" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
+      <c r="I9" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="46"/>
+    </row>
+    <row r="10" spans="2:10" ht="54" x14ac:dyDescent="0.25">
+      <c r="B10" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -30145,9 +30209,11 @@
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="2:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+    </row>
+    <row r="11" spans="2:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="35"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -30159,12 +30225,14 @@
         <v>54</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+    </row>
+    <row r="12" spans="2:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="35"/>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
@@ -30177,8 +30245,10 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+    </row>
+    <row r="13" spans="2:10" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -30187,43 +30257,43 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="2:8" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
+    <row r="14" spans="2:10" ht="27.75" x14ac:dyDescent="0.35">
+      <c r="B14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="2:8" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>69</v>
+    <row r="15" spans="2:10" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="22" t="s">
+        <v>67</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="B17" s="15" t="s">
-        <v>57</v>
+      <c r="B17" s="19" t="s">
+        <v>56</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>70</v>
+      <c r="B18" s="22" t="s">
+        <v>68</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="10">
